--- a/diseases/d163/2015-2019.xlsx
+++ b/diseases/d163/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.05780601880121494</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>4</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.07707469173495324</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.01926867293373831</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3685,9 +3664,6 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.01926867293373831</v>
       </c>
@@ -4229,9 +4205,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.03853734586747662</v>
       </c>
@@ -4625,9 +4598,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5021,9 +4991,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5417,9 +5384,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5813,9 +5777,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6209,9 +6170,6 @@
       <c r="O30" t="n">
         <v>4</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.04030925258583855</v>
       </c>
@@ -6605,9 +6563,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.03819722103757785</v>
       </c>
@@ -7001,9 +6956,6 @@
       <c r="O34" t="n">
         <v>7</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.07054119202521747</v>
       </c>
@@ -7545,9 +7497,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7941,9 +7890,6 @@
       <c r="O39" t="n">
         <v>6</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.06046387887875783</v>
       </c>
@@ -8485,9 +8431,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8881,9 +8824,6 @@
       <c r="O44" t="n">
         <v>5</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.05038656573229819</v>
       </c>
@@ -9425,9 +9365,6 @@
       <c r="O47" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.03819722103757785</v>
       </c>
@@ -9821,9 +9758,6 @@
       <c r="O49" t="n">
         <v>4</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.04030925258583855</v>
       </c>
@@ -10217,9 +10151,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.01909861051878893</v>
       </c>
@@ -10613,9 +10544,6 @@
       <c r="O53" t="n">
         <v>4</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.04030925258583855</v>
       </c>
@@ -11009,9 +10937,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -11405,9 +11330,6 @@
       <c r="O57" t="n">
         <v>7</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.07054119202521747</v>
       </c>
@@ -11801,9 +11723,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.01909861051878893</v>
       </c>
@@ -12197,9 +12116,6 @@
       <c r="O61" t="n">
         <v>3</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -12593,9 +12509,6 @@
       <c r="O63" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.03819722103757785</v>
       </c>
@@ -12989,9 +12902,6 @@
       <c r="O65" t="n">
         <v>11</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.110850444611056</v>
       </c>
@@ -13385,9 +13295,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13781,9 +13688,6 @@
       <c r="O69" t="n">
         <v>12</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.1209277577575157</v>
       </c>
@@ -14177,9 +14081,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -14573,9 +14474,6 @@
       <c r="O73" t="n">
         <v>11</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.110850444611056</v>
       </c>
@@ -14969,9 +14867,6 @@
       <c r="O75" t="n">
         <v>2</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.03819722103757785</v>
       </c>
@@ -15365,9 +15260,6 @@
       <c r="O77" t="n">
         <v>18</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1813916366362735</v>
       </c>
@@ -15909,9 +15801,6 @@
       <c r="O80" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.03790174068481812</v>
       </c>
@@ -16305,9 +16194,6 @@
       <c r="O82" t="n">
         <v>7</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.06959729958500621</v>
       </c>
@@ -16701,9 +16587,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -17097,9 +16980,6 @@
       <c r="O86" t="n">
         <v>12</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.1193096564314392</v>
       </c>
@@ -17493,9 +17373,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -17889,9 +17766,6 @@
       <c r="O90" t="n">
         <v>11</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.1093671850621526</v>
       </c>
@@ -18285,9 +18159,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.03790174068481812</v>
       </c>
@@ -18681,9 +18552,6 @@
       <c r="O94" t="n">
         <v>9</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.08948224232357942</v>
       </c>
@@ -19077,9 +18945,6 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -19473,9 +19338,6 @@
       <c r="O98" t="n">
         <v>5</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.04971235684643301</v>
       </c>
@@ -19869,9 +19731,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -20265,9 +20124,6 @@
       <c r="O102" t="n">
         <v>11</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.1093671850621526</v>
       </c>
@@ -20661,9 +20517,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -21057,9 +20910,6 @@
       <c r="O106" t="n">
         <v>18</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.1789644846471588</v>
       </c>
@@ -21453,9 +21303,6 @@
       <c r="O108" t="n">
         <v>3</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.05685261102722718</v>
       </c>
@@ -21849,9 +21696,6 @@
       <c r="O110" t="n">
         <v>25</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2485617842321651</v>
       </c>
@@ -22245,9 +22089,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -22641,9 +22482,6 @@
       <c r="O114" t="n">
         <v>14</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.1391945991700124</v>
       </c>
@@ -23037,9 +22875,6 @@
       <c r="O116" t="n">
         <v>4</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.07580348136963624</v>
       </c>
@@ -23433,9 +23268,6 @@
       <c r="O118" t="n">
         <v>6</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.05965482821571962</v>
       </c>
@@ -23829,9 +23661,6 @@
       <c r="O120" t="n">
         <v>6</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.1137052220544544</v>
       </c>
@@ -24225,9 +24054,6 @@
       <c r="O122" t="n">
         <v>8</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.07953977095429282</v>
       </c>
@@ -24621,9 +24447,6 @@
       <c r="O124" t="n">
         <v>4</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.07580348136963624</v>
       </c>
@@ -25017,9 +24840,6 @@
       <c r="O126" t="n">
         <v>32</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.3181590838171713</v>
       </c>
@@ -25413,9 +25233,6 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.037652356731606</v>
       </c>
@@ -25809,9 +25626,6 @@
       <c r="O130" t="n">
         <v>23</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.2260352401715333</v>
       </c>
@@ -26205,9 +26019,6 @@
       <c r="O132" t="n">
         <v>2</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.037652356731606</v>
       </c>
@@ -26601,9 +26412,6 @@
       <c r="O134" t="n">
         <v>28</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.275173335860997</v>
       </c>
@@ -26997,9 +26805,6 @@
       <c r="O136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.037652356731606</v>
       </c>
@@ -27393,9 +27198,6 @@
       <c r="O138" t="n">
         <v>12</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.117931429654713</v>
       </c>
@@ -27937,9 +27739,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -28333,9 +28132,6 @@
       <c r="O143" t="n">
         <v>16</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.157241906206284</v>
       </c>
@@ -28729,9 +28525,6 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -29125,9 +28918,6 @@
       <c r="O147" t="n">
         <v>11</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.1081038105168202</v>
       </c>
@@ -29521,9 +29311,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -29917,9 +29704,6 @@
       <c r="O151" t="n">
         <v>14</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.1375866679304985</v>
       </c>
@@ -30313,9 +30097,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -30709,9 +30490,6 @@
       <c r="O155" t="n">
         <v>13</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.1277590487926057</v>
       </c>
@@ -31105,9 +30883,6 @@
       <c r="O157" t="n">
         <v>2</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.037652356731606</v>
       </c>
@@ -31501,9 +31276,6 @@
       <c r="O159" t="n">
         <v>27</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.2653457167231043</v>
       </c>
@@ -31897,9 +31669,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -32293,9 +32062,6 @@
       <c r="O163" t="n">
         <v>11</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.1081038105168202</v>
       </c>
@@ -32689,9 +32455,6 @@
       <c r="O165" t="n">
         <v>6</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.112957070194818</v>
       </c>
@@ -33085,9 +32848,6 @@
       <c r="O167" t="n">
         <v>17</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.1670695253441767</v>
       </c>
@@ -33481,9 +33241,6 @@
       <c r="O169" t="n">
         <v>4</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.07530471346321199</v>
       </c>
@@ -33877,9 +33634,6 @@
       <c r="O171" t="n">
         <v>32</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.314483812412568</v>
       </c>
@@ -34273,9 +34027,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -34669,9 +34420,6 @@
       <c r="O175" t="n">
         <v>39</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.3832771463778172</v>
       </c>
@@ -35065,9 +34813,6 @@
       <c r="O177" t="n">
         <v>3</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.0560985636804248</v>
       </c>
@@ -35461,9 +35206,6 @@
       <c r="O179" t="n">
         <v>28</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.2723967263750562</v>
       </c>
@@ -35857,9 +35599,6 @@
       <c r="O181" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.03739904245361654</v>
       </c>
@@ -36253,9 +35992,6 @@
       <c r="O183" t="n">
         <v>21</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.2042975447812922</v>
       </c>
@@ -36649,9 +36385,6 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -37045,9 +36778,6 @@
       <c r="O187" t="n">
         <v>7</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.06809918159376406</v>
       </c>
@@ -37441,9 +37171,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -37837,9 +37564,6 @@
       <c r="O191" t="n">
         <v>21</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.2042975447812922</v>
       </c>
@@ -38233,9 +37957,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -38629,9 +38350,6 @@
       <c r="O195" t="n">
         <v>8</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.07782763610715893</v>
       </c>
@@ -39025,9 +38743,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -39421,9 +39136,6 @@
       <c r="O199" t="n">
         <v>7</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.06809918159376406</v>
       </c>
@@ -39817,9 +39529,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -40213,9 +39922,6 @@
       <c r="O203" t="n">
         <v>6</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.0583707270803692</v>
       </c>
@@ -40609,9 +40315,6 @@
       <c r="O205" t="n">
         <v>1</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -41005,9 +40708,6 @@
       <c r="O207" t="n">
         <v>13</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.1264699086741333</v>
       </c>
@@ -41549,9 +41249,6 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -41945,9 +41642,6 @@
       <c r="O212" t="n">
         <v>9</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.08755609062055379</v>
       </c>
@@ -42341,9 +42035,6 @@
       <c r="O214" t="n">
         <v>2</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.03739904245361654</v>
       </c>
@@ -42737,9 +42428,6 @@
       <c r="O216" t="n">
         <v>8</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.07782763610715893</v>
       </c>
@@ -43133,9 +42821,6 @@
       <c r="O218" t="n">
         <v>1</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -43529,9 +43214,6 @@
       <c r="O220" t="n">
         <v>16</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.1556552722143179</v>
       </c>
@@ -44073,9 +43755,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -44468,9 +44147,6 @@
       </c>
       <c r="O225" t="n">
         <v>11</v>
-      </c>
-      <c r="Q225" t="n">
-        <v>0</v>
       </c>
       <c r="R225" t="n">
         <v>0.1070129996473435</v>
